--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,26 @@
         <is>
           <t>Treinos</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marcos Felix</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2,006,2 km</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>31.791 m</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2,006,2 km</t>
+          <t>2.006,2 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.006,2 km</t>
+          <t>2,006,2 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,6 +468,26 @@
       </c>
       <c r="D2" t="n">
         <v>138</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Juliana Nogueira</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>250,2 km</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.758 m</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,46 +450,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Marcos Felix</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2.006,2 km</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>31.791 m</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Juliana Nogueira</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>250,2 km</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2.758 m</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>70</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,46 @@
         <is>
           <t>Treinos</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marcos Felix</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.006,2 km</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>31.791 m</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Juliana Nogueira</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>250,2 km</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.758 m</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +473,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Cristiano Silva</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>362,1 km</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.643 m</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Juliana Nogueira</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>250,2 km</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2.758 m</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>70</v>
       </c>
     </row>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -1,37 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos Felix\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="8868"/>
   </bookViews>
   <sheets>
-    <sheet name="Ranking CNB 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ranking CNB 2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Atleta</t>
+  </si>
+  <si>
+    <t>KM Total</t>
+  </si>
+  <si>
+    <t>Altimetria (m)</t>
+  </si>
+  <si>
+    <t>Treinos</t>
+  </si>
+  <si>
+    <t>Marcos Felix</t>
+  </si>
+  <si>
+    <t>Cristiano Silva</t>
+  </si>
+  <si>
+    <t>362,1 km</t>
+  </si>
+  <si>
+    <t>2.643 m</t>
+  </si>
+  <si>
+    <t>Juliana Nogueira</t>
+  </si>
+  <si>
+    <t>250,2 km</t>
+  </si>
+  <si>
+    <t>2.758 m</t>
+  </si>
+  <si>
+    <t>2.005,5 km</t>
+  </si>
+  <si>
+    <t>31.787 m</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +95,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,93 +419,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Atleta</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>KM Total</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Altimetria (m)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Treinos</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Marcos Felix</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2.006,2 km</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>31.791 m</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>138</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>137</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cristiano Silva</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>362,1 km</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2.643 m</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
         <v>48</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Juliana Nogueira</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>250,2 km</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2.758 m</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
         <v>70</v>
       </c>
     </row>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -1,86 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos Felix\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="8868"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ranking CNB 2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Ranking CNB 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Atleta</t>
-  </si>
-  <si>
-    <t>KM Total</t>
-  </si>
-  <si>
-    <t>Altimetria (m)</t>
-  </si>
-  <si>
-    <t>Treinos</t>
-  </si>
-  <si>
-    <t>Marcos Felix</t>
-  </si>
-  <si>
-    <t>Cristiano Silva</t>
-  </si>
-  <si>
-    <t>362,1 km</t>
-  </si>
-  <si>
-    <t>2.643 m</t>
-  </si>
-  <si>
-    <t>Juliana Nogueira</t>
-  </si>
-  <si>
-    <t>250,2 km</t>
-  </si>
-  <si>
-    <t>2.758 m</t>
-  </si>
-  <si>
-    <t>2.005,5 km</t>
-  </si>
-  <si>
-    <t>31.787 m</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -95,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -419,63 +420,93 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Atleta</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>KM Total</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Altimetria (m)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Treinos</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>137</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marcos Felix</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.006,2 km</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>31.791 m</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cristiano Silva</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>362,1 km</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.643 m</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Juliana Nogueira</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>250,2 km</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2.758 m</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>70</v>
       </c>
     </row>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.006,2 km</t>
+          <t>2.005,5 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.791 m</t>
+          <t>31.786 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.005,5 km</t>
+          <t>2.027,5 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.786 m</t>
+          <t>31.967 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
@@ -478,16 +478,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>362,1 km</t>
+          <t>367,4 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.643 m</t>
+          <t>2.698 m</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,40 +473,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cristiano Silva</t>
+          <t>Fabio Oliveira</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>367,4 km</t>
+          <t>866,6 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.698 m</t>
+          <t>9.136 m</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Cristiano Silva</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>367,4 km</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2.698 m</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Juliana Nogueira</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>250,2 km</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2.758 m</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>70</v>
       </c>
     </row>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.027,5 km</t>
+          <t>2.039,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.967 m</t>
+          <t>32.074 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
@@ -478,16 +478,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>866,6 km</t>
+          <t>878,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.136 m</t>
+          <t>9.237 m</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -518,16 +518,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250,2 km</t>
+          <t>253,5 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.758 m</t>
+          <t>2.789 m</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>367,4 km</t>
+          <t>371,9 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.698 m</t>
+          <t>2.751 m</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>371,9 km</t>
+          <t>372,3 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.751 m</t>
+          <t>2.793 m</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.039,7 km</t>
+          <t>2.048,3 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.074 m</t>
+          <t>32.179 m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -498,16 +498,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>372,3 km</t>
+          <t>376,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.793 m</t>
+          <t>2.795 m</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">

--- a/Ranking_CNB_2026.xlsx
+++ b/Ranking_CNB_2026.xlsx
@@ -478,16 +478,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>878,8 km</t>
+          <t>888,9 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.237 m</t>
+          <t>9.359 m</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
@@ -518,16 +518,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>253,5 km</t>
+          <t>257,2 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.789 m</t>
+          <t>2.826 m</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
